--- a/proposal/chuangzhihui-annual-ops-plan-final.xlsx
+++ b/proposal/chuangzhihui-annual-ops-plan-final.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
